--- a/python-version/examples/template_definitions/空白模板定义.xlsx
+++ b/python-version/examples/template_definitions/空白模板定义.xlsx
@@ -9,24 +9,36 @@
   <sheets>
     <sheet name="填写说明" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="输入参数" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="原始测量" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="派生指标与公式" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="优化目标" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="先验关系" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="输入约束" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="输出约束" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="模板设置" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="_填写选项" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet name="原始测量" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="派生指标与公式" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="优化目标" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="先验关系" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="输入约束" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="输出约束" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="模板设置" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'填写说明'!$A$1:$A$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'输入参数'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'原始测量'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'派生指标与公式'!$A$1:$T$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'优化目标'!$A$1:$E$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'先验关系'!$A$1:$H$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'输入约束'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'输出约束'!$A$1:$D$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'模板设置'!$A$1:$C$8</definedName>
+    <definedName name="_planner_options_1">'_填写选项'!$A$1:$A$10</definedName>
+    <definedName name="_planner_options_2">'_填写选项'!$B$1:$B$4</definedName>
+    <definedName name="_planner_options_3">'_填写选项'!$C$1:$C$6</definedName>
+    <definedName name="_planner_options_4">'_填写选项'!$D$1:$D$6</definedName>
+    <definedName name="_planner_options_5">'_填写选项'!$E$1:$E$4</definedName>
+    <definedName name="_planner_options_6">'_填写选项'!$F$1:$F$6</definedName>
+    <definedName name="_planner_options_7">'_填写选项'!$G$1:$G$5</definedName>
+    <definedName name="_planner_options_8">'_填写选项'!$H$1:$H$2</definedName>
+    <definedName name="_planner_options_9">'_填写选项'!$I$1:$I$7</definedName>
+    <definedName name="_planner_options_10">'_填写选项'!$J$1:$J$3</definedName>
+    <definedName name="_planner_options_11">'_填写选项'!$K$1:$K$3</definedName>
+    <definedName name="_planner_options_12">'_填写选项'!$L$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'输入参数'!$A$2:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'原始测量'!$A$2:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'派生指标与公式'!$A$2:$T$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'优化目标'!$A$2:$E$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'先验关系'!$A$2:$H$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'输入约束'!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'输出约束'!$A$2:$D$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'模板设置'!$A$2:$D$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +47,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,16 +56,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <color rgb="00B91C1C"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <color rgb="0078350F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -73,9 +98,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -150,6 +186,546 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：英文字母开头，仅字母、数字、下划线；所有字段表不得重名。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：显示名称；留空使用内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：自由输入单位；留空为 1（无量纲），不自动换算自定义单位。</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：字段说明。</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：用范围定义数值输入时，下限和上限都要填，且下限 &lt; 上限。范围、离散值、固定值三选一。</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：范围输入的上限；必须大于下限。无范围时留空。</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：类别输入需要离散值或固定值；填写 JSON 数组，例如 ["甲","乙"] 或 [1,2,3]。</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：固定输入只填该值，不再填范围或离散值；按字段类型填写。</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>留空：本区域不填写派生公式。</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：none 不限制、digits 小数位数、step 步长。仅数值输入使用；空白默认 none。</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：digits 模式填整数，-12 ≤ 位数 ≤ 12；不用时留空。</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：step 模式的步长，数值 &gt; 0。</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：step 网格起点，任意有限数值；留空为 0。</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：英文字母开头，仅字母、数字、下划线；所有字段表不得重名。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：显示名称；留空使用内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：自由输入单位；留空为 1（无量纲），不自动换算自定义单位。</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：字段说明。</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：类别测量填写允许值的 JSON 数组，例如 ["甲","乙"]。</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>留空：本区域不填写派生公式。</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：英文字母开头，仅字母、数字、下划线；所有字段表不得重名。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：显示名称；留空使用内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：自由输入单位；留空为 1（无量纲），不自动换算自定义单位。</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：字段说明。</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：类别测量填写允许值的 JSON 数组，例如 ["甲","乙"]。</t>
+      </text>
+    </comment>
+    <comment ref="I2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="J2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+      </text>
+    </comment>
+    <comment ref="K2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。</t>
+      </text>
+    </comment>
+    <comment ref="L2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。</t>
+      </text>
+    </comment>
+    <comment ref="M2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。</t>
+      </text>
+    </comment>
+    <comment ref="N2" authorId="0" shapeId="0">
+      <text>
+        <t>必填（派生指标）：用内部名称写公式，例如 quality * 2。其他字段留空。</t>
+      </text>
+    </comment>
+    <comment ref="O2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。</t>
+      </text>
+    </comment>
+    <comment ref="P2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="Q2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="R2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="S2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+      </text>
+    </comment>
+    <comment ref="T2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：已有响应或派生指标的内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：maximize 尽量大、minimize 尽量小；留空为 maximize。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：identity 原值、abs 绝对值、absolute_distance 距指定值的距离；留空为 identity。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：变换为 absolute_distance 时的目标值；任意有限数值。</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：true/是 启用、false/否 不启用；留空默认启用。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>启用时必填：数值模型输入的内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>启用时必填：直接建模基础响应的内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>启用时必填：independent 独立、linear 线性、proportional 比例、monotonic 单调、weak 弱先验。</t>
+      </text>
+    </comment>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：启用非 independent/weak 关系时填有符号系数；任意有限数值，单位为响应单位/输入单位。</t>
+      </text>
+    </comment>
+    <comment ref="F2" authorId="0" shapeId="0">
+      <text>
+        <t>条件必填：启用非 independent 关系时的强度，数值 &gt; 0。</t>
+      </text>
+    </comment>
+    <comment ref="G2" authorId="0" shapeId="0">
+      <text>
+        <t>启用时必填：经验或文献依据。</t>
+      </text>
+    </comment>
+    <comment ref="H2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：非空 JSON 系数组，例如 {"speed":1}；内部名称须是数值输入。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：从下拉选 &lt;=（不超过）或 &gt;=（不低于）。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：输入约束阈值，任意有限数值。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：已有响应或派生指标的内部名称。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：从下拉选 &lt;=（不超过）或 &gt;=（不低于）。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：输出约束阈值，任意有限数值。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>实验规划助手</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>必填：属性路径，例如 name、optimization.mode。全新实验删除无关的旧元数据行。</t>
+      </text>
+    </comment>
+    <comment ref="B2" authorId="0" shapeId="0">
+      <text>
+        <t>必填或选填见本行右侧说明；存在固定选项时从下拉选择。列表/对象填写 JSON。</t>
+      </text>
+    </comment>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>选填：str 文字 / int 整数 / float 数值 / bool 是否 / list 列表 / dict 对象 / null 空值。</t>
+      </text>
+    </comment>
+    <comment ref="D2" authorId="0" shapeId="0">
+      <text>
+        <t>仅供阅读：本行的必填条件、范围、作用；本列不导入模板配置。</t>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0">
+      <text>
+        <t>必填：格式版本，固定为整数 2。</t>
+      </text>
+    </comment>
+    <comment ref="B4" authorId="0" shapeId="0">
+      <text>
+        <t>必填：模板版本，整数 ≥ 1。</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
+        <t>模板名称，可自由修改。</t>
+      </text>
+    </comment>
+    <comment ref="B6" authorId="0" shapeId="0">
+      <text>
+        <t>必填：pareto 多目标折中；single 恰好一个有效目标；weighted 配合 weights/scales 的 JSON 数组。</t>
+      </text>
+    </comment>
+    <comment ref="B7" authorId="0" shapeId="0">
+      <text>
+        <t>默认模型：gp_rbf_v1 RBF、gp_matern25_v1 Matérn 2.5、bayesian_linear_v1 贝叶斯线性。</t>
+      </text>
+    </comment>
+    <comment ref="B8" authorId="0" shapeId="0">
+      <text>
+        <t>remove 移除指定比值目标；stabilized 稳定化；valid_region 有效区域；require_configuration 待配置。</t>
+      </text>
+    </comment>
+    <comment ref="B9" authorId="0" shapeId="0">
+      <text>
+        <t>选填：列表/对象写 JSON；字段引用须改为本实验的内部名称。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -441,14 +1017,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="65" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>本文件定义实验模板，不是实验记录导入表。可导入“新建 / 复制 / 修改模板”继续编辑。</t>
         </is>
@@ -464,97 +1040,346 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>类型填 float/int/category/bool/text，或 数值/整数/类别/是否/文字。单位可自由填写，无量纲填 1。</t>
+          <t>各表第 1 行是填写提示，第 2 行是列名，第 3 行起填数据；不要修改表头。固定选项有下拉，数值限定见列名上方。</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>数值输入填写下限/上限，或离散值，或固定值；这三种方式选一种。是否输入可全部留空。</t>
+          <t>必填与条件必填在提示行标出；限定覆盖 10000 行。复制粘贴可能绕过 Excel 校验，导入和最终保存仍由软件校验。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>离散值可写 JSON 数组（例如 [1,2,3] 或 ["甲","乙"]），也可用中英文逗号分隔。</t>
+          <t>类型填 float/int/category/bool/text，或 数值/整数/类别/是否/文字。单位可自由填写，无量纲填 1。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>文字输入不进入数值模型；可自由填写，推荐时需基准文字或固定值/离散值。</t>
+          <t>数值输入填写下限/上限，或离散值，或固定值；这三种方式选一种。是否输入可全部留空。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>开关列填 是/否 或 true/false；文字/类别测量的作为响应填否。</t>
+          <t>离散值可写 JSON 数组（例如 [1,2,3] 或 ["甲","乙"]），也可用中英文逗号分隔。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>原始测量作为响应、直接建模默认是；派生指标作为响应默认是、直接建模默认否。</t>
+          <t>文字输入不进入数值模型；可自由填写，推荐时需基准文字或固定值/离散值。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>派生公式使用内部名称，例如 result * 2；可写 =result * 2，导入只解析文字，不执行 Excel 公式。</t>
+          <t>开关列填 是/否 或 true/false；文字/类别测量的作为响应填否。</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>至少一个输入、一个直接建模的响应、一个有效目标。目标方向填 maximize/minimize 或 尽量大/尽量小。</t>
+          <t>原始测量作为响应、直接建模默认是；派生指标作为响应默认是、直接建模默认否。</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>模板设置每行一个属性路径，例如 name、optimization.mode（pareto/single/weighted）、ratio_policy.mode。</t>
+          <t>派生公式使用内部名称，例如 result * 2；可写 =result * 2，导入只解析文字，不执行 Excel 公式。</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>模板设置的列表/对象填写 JSON；加权模式用 optimization.weights/scales，顺序对应有效目标。</t>
+          <t>至少一个输入、一个直接建模的响应、一个有效目标。目标方向填 maximize/minimize 或 尽量大/尽量小。</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>其他属性可留空；用于保留扩展 JSON 配置。输入约束系数示例：{"speed":1}。</t>
+          <t>模板设置每行一个属性路径，例如 name、optimization.mode（pareto/single/weighted）、ratio_policy.mode。</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>留空属性表示待填写，可先导入编辑；最终保存时校验类型、范围、公式量纲和优化目标。</t>
+          <t>模板设置的列表/对象填写 JSON；加权模式用 optimization.weights/scales，顺序对应有效目标。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>其他属性可留空；用于保留扩展 JSON 配置。输入约束系数示例：{"speed":1}。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>留空属性表示待填写，可先导入编辑；最终保存时校验类型、范围、公式量纲和优化目标。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>显示小数位数仅改变显示；执行模式 digits 配合执行小数位数，step 配合步长与网格起点。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="110" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>【填写提示】必填：属性路径，例如 name、optimization.mode。全新实验删除无关的旧元数据行。</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>必填或选填见本行右侧说明；存在固定选项时从下拉选择。列表/对象填写 JSON。</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>选填：str 文字 / int 整数 / float 数值 / bool 是否 / list 列表 / dict 对象 / null 空值。</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>仅供阅读：本行的必填条件、范围、作用；本列不导入模板配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>属性</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>类型（可留空）</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>填写说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="55" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>必填：格式版本，固定为整数 2。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>template_version</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>必填：模板版本，整数 ≥ 1。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>全新实验模板</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>模板名称，可自由修改。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>optimization.mode</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>pareto</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>必填：pareto 多目标折中；single 恰好一个有效目标；weighted 配合 weights/scales 的 JSON 数组。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>optimization.default_model_preset</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>gp_rbf_v1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>默认模型：gp_rbf_v1 RBF、gp_matern25_v1 Matérn 2.5、bayesian_linear_v1 贝叶斯线性。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ratio_policy.mode</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>remove 移除指定比值目标；stabilized 稳定化；valid_region 有效区域；require_configuration 待配置。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>batch_defaults</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>dict</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>选填：列表/对象写 JSON；字段引用须改为本实验的内部名称。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D9"/>
+  <dataValidations count="6">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="属性值的类型；留空按 JSON 或文字解析。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_9</formula1>
+    </dataValidation>
+    <dataValidation sqref="B3" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：格式版本，固定为整数 2。" type="custom" errorStyle="stop">
+      <formula1>OR(B3="",AND(ISNUMBER(B3),B3=INT(B3),B3&gt;=2,B3&lt;=2))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：模板版本，整数 ≥ 1。" type="custom" errorStyle="stop">
+      <formula1>OR(B4="",AND(ISNUMBER(B4),B4=INT(B4),B4&gt;=1))</formula1>
+    </dataValidation>
+    <dataValidation sqref="B6" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：pareto 多目标折中；single 恰好一个有效目标；weighted 配合 weights/scales 的 JSON 数组。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_10</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="默认模型：gp_rbf_v1 RBF、gp_matern25_v1 Matérn 2.5、bayesian_linear_v1 贝叶斯线性。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_11</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="remove 移除指定比值目标；stabilized 稳定化；valid_region 有效区域；require_configuration 待配置。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_12</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -564,136 +1389,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>【填写提示】必填：英文字母开头，仅字母、数字、下划线；所有字段表不得重名。</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>选填：显示名称；留空使用内部名称。</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>选填：自由输入单位；留空为 1（无量纲），不自动换算自定义单位。</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>选填：字段说明。</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：用范围定义数值输入时，下限和上限都要填，且下限 &lt; 上限。范围、离散值、固定值三选一。</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：范围输入的上限；必须大于下限。无范围时留空。</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：类别输入需要离散值或固定值；填写 JSON 数组，例如 ["甲","乙"] 或 [1,2,3]。</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>选填：固定输入只填该值，不再填范围或离散值；按字段类型填写。</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>留空：本区域不填写派生公式。</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>选填：none 不限制、digits 小数位数、step 步长。仅数值输入使用；空白默认 none。</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：digits 模式填整数，-12 ≤ 位数 ≤ 12；不用时留空。</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：step 模式的步长，数值 &gt; 0。</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>选填：step 网格起点，任意有限数值；留空为 0。</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>内部名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>显示名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>下限</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>上限</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>离散值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>作为模型输入</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>作为响应</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>直接建模</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>测量时点</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>计算公式</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>显示小数位数</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>执行模式</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>执行小数位数</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>步长</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>网格起点</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1"/>
+  <autoFilter ref="A2:T2"/>
+  <dataValidations count="12">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_1</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：用范围定义数值输入时，下限和上限都要填，且下限 &lt; 上限。范围、离散值、固定值三选一。" type="custom" errorStyle="stop">
+      <formula1>OR(F3="",AND(ISNUMBER(F3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：范围输入的上限；必须大于下限。无范围时留空。" type="custom" errorStyle="stop">
+      <formula1>OR(G3="",AND(ISNUMBER(G3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_3</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。" type="custom" errorStyle="stop">
+      <formula1>OR(O3="",AND(ISNUMBER(O3),O3=INT(O3),O3&gt;=-12,O3&lt;=12))</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：none 不限制、digits 小数位数、step 步长。仅数值输入使用；空白默认 none。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_4</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：digits 模式填整数，-12 ≤ 位数 ≤ 12；不用时留空。" type="custom" errorStyle="stop">
+      <formula1>OR(Q3="",AND(ISNUMBER(Q3),Q3=INT(Q3),Q3&gt;=-12,Q3&lt;=12))</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3:R10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：step 模式的步长，数值 &gt; 0。" type="custom" errorStyle="stop">
+      <formula1>OR(R3="",AND(ISNUMBER(R3),R3&gt;0))</formula1>
+    </dataValidation>
+    <dataValidation sqref="S3:S10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：step 网格起点，任意有限数值；留空为 0。" type="custom" errorStyle="stop">
+      <formula1>OR(S3="",AND(ISNUMBER(S3)))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -703,135 +1669,330 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:L10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>内部名称</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>显示名称</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>单位</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>下限</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>上限</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>离散值</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>固定值</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>作为模型输入</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>作为响应</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>直接建模</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>测量时点</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>计算公式</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>显示小数位数</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>执行模式</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>执行小数位数</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>步长</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>网格起点</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>其他属性</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>before</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>maximize</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>identity</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>independent</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>&lt;=</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>str</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pareto</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>gp_rbf_v1</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>after</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>digits</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>minimize</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>abs</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>single</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>gp_matern25_v1</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>stabilized</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>step</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>尽量大</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>absolute_distance</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>proportional</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>weighted</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bayesian_linear_v1</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>valid_region</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>实验前</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>不限制</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>尽量小</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>原值</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>monotonic</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>require_configuration</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>实验后</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>小数位数</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>绝对值</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>weak</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>未指定</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>指定步长</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>距指定值的距离</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>dict</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>整数</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>类别</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>是否</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>文字</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -842,136 +2003,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="16" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>【填写提示】必填：英文字母开头，仅字母、数字、下划线；所有字段表不得重名。</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>选填：显示名称；留空使用内部名称。</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>选填：自由输入单位；留空为 1（无量纲），不自动换算自定义单位。</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>选填：字段说明。</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：类别测量填写允许值的 JSON 数组，例如 ["甲","乙"]。</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>留空：本区域不填写派生公式。</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
           <t>内部名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>显示名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>单位</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>说明</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>下限</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>上限</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>离散值</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>作为模型输入</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>作为响应</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>直接建模</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>测量时点</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>计算公式</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>显示小数位数</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P2" s="3" t="inlineStr">
         <is>
           <t>执行模式</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>执行小数位数</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>步长</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>网格起点</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T1"/>
+  <autoFilter ref="A2:T2"/>
+  <dataValidations count="12">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_1</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(F3="",AND(ISNUMBER(F3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(G3="",AND(ISNUMBER(G3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_3</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。" type="custom" errorStyle="stop">
+      <formula1>OR(O3="",AND(ISNUMBER(O3),O3=INT(O3),O3&gt;=-12,O3&lt;=12))</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_4</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(Q3="",AND(ISNUMBER(Q3),Q3=INT(Q3),Q3&gt;=-12,Q3&lt;=12))</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3:R10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(R3="",AND(ISNUMBER(R3),R3&gt;0))</formula1>
+    </dataValidation>
+    <dataValidation sqref="S3:S10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(S3="",AND(ISNUMBER(S3)))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -981,46 +2283,277 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="24" customWidth="1" min="19" max="19"/>
+    <col width="24" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>响应或指标</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>方向</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>变换</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>目标值</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
+          <t>【填写提示】必填：英文字母开头，仅字母、数字、下划线；所有字段表不得重名。</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>选填：显示名称；留空使用内部名称。</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>选填：自由输入单位；留空为 1（无量纲），不自动换算自定义单位。</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>选填：字段说明。</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：类别测量填写允许值的 JSON 数组，例如 ["甲","乙"]。</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>必填（派生指标）：用内部名称写公式，例如 quality * 2。其他字段留空。</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。</t>
+        </is>
+      </c>
+      <c r="P1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="R1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="S1" s="2" t="inlineStr">
+        <is>
+          <t>选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。</t>
+        </is>
+      </c>
+      <c r="T1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>内部名称</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>显示名称</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>单位</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>下限</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>上限</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>离散值</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>作为模型输入</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>作为响应</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>直接建模</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>测量时点</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>计算公式</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr">
+        <is>
+          <t>显示小数位数</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>执行模式</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>执行小数位数</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>步长</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>网格起点</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
         <is>
           <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A2:T2"/>
+  <dataValidations count="12">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_1</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(F3="",AND(ISNUMBER(F3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="G3:G10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(G3="",AND(ISNUMBER(G3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3:K10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="L3:L10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：直接建模？原始测量手写留空默认是；派生指标留空默认否。至少一个响应需直接建模。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="M3:M10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：测量时点 before/实验前、after/实验后、unknown/未指定。手写原始测量留空默认 after。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_3</formula1>
+    </dataValidation>
+    <dataValidation sqref="O3:O10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：整数范围 -12 ≤ 位数 ≤ 12；空白为原始精度，仅改变显示。" type="custom" errorStyle="stop">
+      <formula1>OR(O3="",AND(ISNUMBER(O3),O3=INT(O3),O3&gt;=-12,O3&lt;=12))</formula1>
+    </dataValidation>
+    <dataValidation sqref="P3:P10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_4</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q3:Q10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(Q3="",AND(ISNUMBER(Q3),Q3=INT(Q3),Q3&gt;=-12,Q3&lt;=12))</formula1>
+    </dataValidation>
+    <dataValidation sqref="R3:R10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(R3="",AND(ISNUMBER(R3),R3&gt;0))</formula1>
+    </dataValidation>
+    <dataValidation sqref="S3:S10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
+      <formula1>OR(S3="",AND(ISNUMBER(S3)))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1030,64 +2563,85 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>启用</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>输入参数</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>基础响应</t>
+          <t>【填写提示】必填：已有响应或派生指标的内部名称。</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>选填：maximize 尽量大、minimize 尽量小；留空为 maximize。</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>选填：identity 原值、abs 绝对值、absolute_distance 距指定值的距离；留空为 identity。</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>关系</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>系数</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>强度</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+          <t>条件必填：变换为 absolute_distance 时的目标值；任意有限数值。</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>响应或指标</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>变换</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>目标值</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1"/>
+  <autoFilter ref="A2:E2"/>
+  <dataValidations count="3">
+    <dataValidation sqref="B3:B10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：maximize 尽量大、minimize 尽量小；留空为 maximize。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_5</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：identity 原值、abs 绝对值、absolute_distance 距指定值的距离；留空为 identity。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_6</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：变换为 absolute_distance 时的目标值；任意有限数值。" type="custom" errorStyle="stop">
+      <formula1>OR(D3="",AND(ISNUMBER(D3)))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1097,40 +2651,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="110" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>【填写提示】选填：true/是 启用、false/否 不启用；留空默认启用。</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>启用时必填：数值模型输入的内部名称。</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>启用时必填：直接建模基础响应的内部名称。</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>启用时必填：independent 独立、linear 线性、proportional 比例、monotonic 单调、weak 弱先验。</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：启用非 independent/weak 关系时填有符号系数；任意有限数值，单位为响应单位/输入单位。</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>条件必填：启用非 independent 关系时的强度，数值 &gt; 0。</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>启用时必填：经验或文献依据。</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>启用</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>输入参数</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>基础响应</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>关系</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>系数</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>比较</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>阈值</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>强度</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>来源</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A2:H2"/>
+  <dataValidations count="4">
+    <dataValidation sqref="A3:A10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 启用、false/否 不启用；留空默认启用。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_2</formula1>
+    </dataValidation>
+    <dataValidation sqref="D3:D10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="启用时必填：independent 独立、linear 线性、proportional 比例、monotonic 单调、weak 弱先验。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_7</formula1>
+    </dataValidation>
+    <dataValidation sqref="E3:E10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：启用非 independent/weak 关系时填有符号系数；任意有限数值，单位为响应单位/输入单位。" type="custom" errorStyle="stop">
+      <formula1>OR(E3="",AND(ISNUMBER(E3)))</formula1>
+    </dataValidation>
+    <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：启用非 independent 关系时的强度，数值 &gt; 0。" type="custom" errorStyle="stop">
+      <formula1>OR(F3="",AND(ISNUMBER(F3),F3&gt;0))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1140,40 +2775,71 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>响应或指标</t>
+          <t>【填写提示】必填：非空 JSON 系数组，例如 {"speed":1}；内部名称须是数值输入。</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>必填：从下拉选 &lt;=（不超过）或 &gt;=（不低于）。</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>必填：输入约束阈值，任意有限数值。</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>系数</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
           <t>比较</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>阈值</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A2:D2"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B3:B10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：从下拉选 &lt;=（不超过）或 &gt;=（不低于）。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_8</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：输入约束阈值，任意有限数值。" type="custom" errorStyle="stop">
+      <formula1>OR(C3="",AND(ISNUMBER(C3)))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -1183,148 +2849,70 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="110" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>属性</t>
+          <t>【填写提示】必填：已有响应或派生指标的内部名称。</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>值</t>
+          <t>必填：从下拉选 &lt;=（不超过）或 &gt;=（不低于）。</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>类型（可留空）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>schema_version</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>template_version</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>全新实验模板</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>optimization.mode</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>pareto</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>optimization.default_model_preset</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>gp_rbf_v1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>ratio_policy.mode</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>remove</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>str</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>batch_defaults</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>dict</t>
+          <t>必填：输出约束阈值，任意有限数值。</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>选填：扩展属性 JSON 对象；不清楚可留空。</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="32" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>响应或指标</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>比较</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>阈值</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>其他属性</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8"/>
+  <autoFilter ref="A2:D2"/>
+  <dataValidations count="2">
+    <dataValidation sqref="B3:B10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：从下拉选 &lt;=（不超过）或 &gt;=（不低于）。" type="list" errorStyle="stop">
+      <formula1>=_planner_options_8</formula1>
+    </dataValidation>
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="必填：输出约束阈值，任意有限数值。" type="custom" errorStyle="stop">
+      <formula1>OR(C3="",AND(ISNUMBER(C3)))</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/python-version/examples/template_definitions/空白模板定义.xlsx
+++ b/python-version/examples/template_definitions/空白模板定义.xlsx
@@ -19,8 +19,8 @@
     <sheet name="模板设置" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
-    <definedName name="_planner_options_1">'_填写选项'!$A$1:$A$10</definedName>
-    <definedName name="_planner_options_2">'_填写选项'!$B$1:$B$4</definedName>
+    <definedName name="_planner_options_1">'_填写选项'!$A$1:$A$9</definedName>
+    <definedName name="_planner_options_2">'_填写选项'!$B$1:$B$2</definedName>
     <definedName name="_planner_options_3">'_填写选项'!$C$1:$C$6</definedName>
     <definedName name="_planner_options_4">'_填写选项'!$D$1:$D$6</definedName>
     <definedName name="_planner_options_5">'_填写选项'!$E$1:$E$4</definedName>
@@ -206,7 +206,7 @@
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
-        <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+        <t>选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
@@ -241,7 +241,7 @@
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+        <t>选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
@@ -316,7 +316,7 @@
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
-        <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+        <t>选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
@@ -351,7 +351,7 @@
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+        <t>选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
@@ -426,7 +426,7 @@
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
-        <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+        <t>选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
@@ -461,7 +461,7 @@
     </comment>
     <comment ref="J2" authorId="0" shapeId="0">
       <text>
-        <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+        <t>选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
       </text>
     </comment>
     <comment ref="K2" authorId="0" shapeId="0">
@@ -561,7 +561,7 @@
   <commentList>
     <comment ref="A2" authorId="0" shapeId="0">
       <text>
-        <t>选填：true/是 启用、false/否 不启用；留空默认启用。</t>
+        <t>选填：是 启用、否 不启用；留空默认启用。</t>
       </text>
     </comment>
     <comment ref="B2" authorId="0" shapeId="0">
@@ -681,7 +681,7 @@
     </comment>
     <comment ref="C2" authorId="0" shapeId="0">
       <text>
-        <t>选填：str 文字 / int 整数 / float 数值 / bool 是否 / list 列表 / dict 对象 / null 空值。</t>
+        <t>选填：str 文字 / int 整数 / float 数值 / 是否 / list 列表 / dict 对象 / null 空值。</t>
       </text>
     </comment>
     <comment ref="D2" authorId="0" shapeId="0">
@@ -1054,7 +1054,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>类型填 float/int/category/bool/text，或 数值/整数/类别/是否/文字。单位可自由填写，无量纲填 1。</t>
+          <t>类型可选数值/整数/类别/是否/文字；是否的填写值选是或否。单位可自由填写，无量纲填 1。</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>开关列填 是/否 或 true/false；文字/类别测量的作为响应填否。</t>
+          <t>开关列只需选 是/否；是否类型的固定值填是或否，离散值可写 ["是","否"]。文字/类别测量的作为响应填否。</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>选填：str 文字 / int 整数 / float 数值 / bool 是否 / list 列表 / dict 对象 / null 空值。</t>
+          <t>选填：str 文字 / int 整数 / float 数值 / 是否 / list 列表 / dict 对象 / null 空值。</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+          <t>选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+          <t>选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
   </sheetData>
   <autoFilter ref="A2:T2"/>
   <dataValidations count="12">
-    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。" type="list" errorStyle="stop">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。" type="list" errorStyle="stop">
       <formula1>=_planner_options_1</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：用范围定义数值输入时，下限和上限都要填，且下限 &lt; 上限。范围、离散值、固定值三选一。" type="custom" errorStyle="stop">
@@ -1630,7 +1630,7 @@
     <dataValidation sqref="G3:G10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="条件必填：范围输入的上限；必须大于下限。无范围时留空。" type="custom" errorStyle="stop">
       <formula1>OR(G3="",AND(ISNUMBER(G3)))</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
+    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
       <formula1>=_planner_options_2</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。" type="list" errorStyle="stop">
@@ -1669,7 +1669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1802,11 +1802,6 @@
           <t>category</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>unknown</t>
@@ -1856,12 +1851,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bool</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>否</t>
+          <t>text</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1891,7 +1881,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>bool</t>
+          <t>是否</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1903,7 +1893,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>数值</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1935,7 +1925,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>数值</t>
+          <t>整数</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1962,7 +1952,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>整数</t>
+          <t>类别</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1974,19 +1964,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>类别</t>
+          <t>是否</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
-        <is>
-          <t>是否</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
         <is>
           <t>文字</t>
         </is>
@@ -2041,7 +2024,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+          <t>选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2076,7 +2059,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+          <t>选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
@@ -2235,7 +2218,7 @@
   </sheetData>
   <autoFilter ref="A2:T2"/>
   <dataValidations count="12">
-    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。" type="list" errorStyle="stop">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。" type="list" errorStyle="stop">
       <formula1>=_planner_options_1</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
@@ -2244,7 +2227,7 @@
     <dataValidation sqref="G3:G10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
       <formula1>OR(G3="",AND(ISNUMBER(G3)))</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
+    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
       <formula1>=_planner_options_2</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。" type="list" errorStyle="stop">
@@ -2321,7 +2304,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。</t>
+          <t>选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -2356,7 +2339,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
+          <t>选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
@@ -2515,7 +2498,7 @@
   </sheetData>
   <autoFilter ref="A2:T2"/>
   <dataValidations count="12">
-    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选 float 数值 / int 整数 / category 类别 / bool 是否 / text 文字；留空为 float。" type="list" errorStyle="stop">
+    <dataValidation sqref="C3:C10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：下拉选数值 / 整数 / 类别 / 是否 / 文字；是否类型的值填是或否。留空为 float（数值）。" type="list" errorStyle="stop">
       <formula1>=_planner_options_1</formula1>
     </dataValidation>
     <dataValidation sqref="F3:F10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
@@ -2524,7 +2507,7 @@
     <dataValidation sqref="G3:G10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：非输入字段通常留空。范围和执行网格仅用于可控输入；下限/上限若填写须成对。" type="custom" errorStyle="stop">
       <formula1>OR(G3="",AND(ISNUMBER(G3)))</formula1>
     </dataValidation>
-    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 或 false/否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
+    <dataValidation sqref="J3:J10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：是 或 否。文字不能作为数值模型输入；事后或未知测量不能作为未来输入。" type="list" errorStyle="stop">
       <formula1>=_planner_options_2</formula1>
     </dataValidation>
     <dataValidation sqref="K3:K10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：作为响应？原始测量/派生指标的数值字段手写留空默认是；文字/类别不作数值响应。" type="list" errorStyle="stop">
@@ -2667,7 +2650,7 @@
     <row r="1" ht="110" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>【填写提示】选填：true/是 启用、false/否 不启用；留空默认启用。</t>
+          <t>【填写提示】选填：是 启用、否 不启用；留空默认启用。</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -2751,7 +2734,7 @@
   </sheetData>
   <autoFilter ref="A2:H2"/>
   <dataValidations count="4">
-    <dataValidation sqref="A3:A10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：true/是 启用、false/否 不启用；留空默认启用。" type="list" errorStyle="stop">
+    <dataValidation sqref="A3:A10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="选填：是 启用、否 不启用；留空默认启用。" type="list" errorStyle="stop">
       <formula1>=_planner_options_2</formula1>
     </dataValidation>
     <dataValidation sqref="D3:D10002" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="填写内容不符合要求" error="请按列名上方说明填写。复制粘贴后仍需通过软件导入校验。" promptTitle="填写说明" prompt="启用时必填：independent 独立、linear 线性、proportional 比例、monotonic 单调、weak 弱先验。" type="list" errorStyle="stop">
